--- a/数据库信息/基础信息/标签字典.xlsx
+++ b/数据库信息/基础信息/标签字典.xlsx
@@ -62,19 +62,19 @@
     <t>延迟退休</t>
   </si>
   <si>
-    <t>共产党员</t>
-  </si>
-  <si>
-    <t>党籍</t>
+    <t>gcdy</t>
+  </si>
+  <si>
+    <t>dj</t>
   </si>
   <si>
     <t>组织关系挂靠</t>
   </si>
   <si>
-    <t>共青团员</t>
-  </si>
-  <si>
-    <t>团籍</t>
+    <t>gqty</t>
+  </si>
+  <si>
+    <t>tj</t>
   </si>
   <si>
     <t>群众</t>
@@ -101,7 +101,7 @@
     <t>退休</t>
   </si>
   <si>
-    <t>死亡</t>
+    <t>去世</t>
   </si>
   <si>
     <t>病休</t>
